--- a/data/trans_orig/Q25_A_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2007</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2007 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29127</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49540</t>
+          <t>50904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34904</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57287</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50797</t>
+          <t>51485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71988</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>34507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29769</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52514</t>
+          <t>53095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>35996</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>41694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66337</t>
+          <t>65155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49860</t>
+          <t>49493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77718</t>
+          <t>79026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51455</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78464</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>46431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>85368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117905</t>
+          <t>118001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35608</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60129</t>
+          <t>59822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35702</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57315</t>
+          <t>58069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87420</t>
+          <t>88946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>48439</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33402</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56320</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>60980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75160</t>
+          <t>74186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47168</t>
+          <t>47385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>25831</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68272</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>21790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>33369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56930</t>
+          <t>55340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47862</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75834</t>
+          <t>74481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60559</t>
+          <t>63119</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86393</t>
+          <t>87293</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48395</t>
+          <t>47998</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96626</t>
+          <t>96224</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128668</t>
+          <t>127354</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57090</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87150</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51897</t>
+          <t>52617</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81653</t>
+          <t>83821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15735</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>59834</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91540</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152066</t>
+          <t>153144</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196547</t>
+          <t>196253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189500</t>
+          <t>187394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>238671</t>
+          <t>238140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>203083</t>
+          <t>204423</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>251209</t>
+          <t>250531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>89833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123294</t>
+          <t>121023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>305080</t>
+          <t>303752</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362843</t>
+          <t>364803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125205</t>
+          <t>124287</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>167489</t>
+          <t>166633</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>108845</t>
+          <t>108434</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>213945</t>
+          <t>211891</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>265436</t>
+          <t>265948</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2012</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2012 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>55109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34432</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37660</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>50966</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>77254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76908</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111266</t>
+          <t>109094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36778</t>
+          <t>35938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60835</t>
+          <t>60320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37391</t>
+          <t>37432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>61528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91619</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31876</t>
+          <t>31799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>58731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35399</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62510</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52431</t>
+          <t>51371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82710</t>
+          <t>81102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34177</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>72757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>109266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63210</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93678</t>
+          <t>93766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20720</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38735</t>
+          <t>38809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127034</t>
+          <t>125468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54868</t>
+          <t>55772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85809</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>31947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52205</t>
+          <t>51709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92777</t>
+          <t>92694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127260</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44047</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>26624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52193</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84830</t>
+          <t>85089</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56777</t>
+          <t>55326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59525</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75739</t>
+          <t>75181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108858</t>
+          <t>108801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>38516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63049</t>
+          <t>64095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29987</t>
+          <t>29829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51844</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75064</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107946</t>
+          <t>108167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>19831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31436</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56642</t>
+          <t>55678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>58100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>35100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53090</t>
+          <t>54465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83771</t>
+          <t>85793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>60693</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88580</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>34980</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55922</t>
+          <t>57072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102250</t>
+          <t>102265</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137644</t>
+          <t>137606</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42516</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69472</t>
+          <t>69066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70546</t>
+          <t>71437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105395</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121860</t>
+          <t>121911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>170673</t>
+          <t>170120</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>142600</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>195129</t>
+          <t>194617</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179416</t>
+          <t>180631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230905</t>
+          <t>233647</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54583</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89270</t>
+          <t>89857</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>247708</t>
+          <t>247914</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>310061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>227904</t>
+          <t>232516</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>284809</t>
+          <t>285037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133430</t>
+          <t>132369</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>173417</t>
+          <t>173771</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>374420</t>
+          <t>379066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>445546</t>
+          <t>447467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>196522</t>
+          <t>195806</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>251189</t>
+          <t>249507</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>121547</t>
+          <t>121524</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>161016</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>333682</t>
+          <t>333130</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>398064</t>
+          <t>396541</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2016</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2016 (tasa de respuesta: 91,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47688</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>29477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50712</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62201</t>
+          <t>61528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55072</t>
+          <t>55976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54366</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80792</t>
+          <t>80197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>36887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>26923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48810</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35820</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61268</t>
+          <t>61055</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45301</t>
+          <t>45284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70994</t>
+          <t>70662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41380</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72148</t>
+          <t>71136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104758</t>
+          <t>103221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60984</t>
+          <t>61931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89687</t>
+          <t>91041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91120</t>
+          <t>90152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126205</t>
+          <t>124741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62939</t>
+          <t>59625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62864</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94342</t>
+          <t>93469</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>42906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25965</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47863</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41905</t>
+          <t>41265</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>68407</t>
+          <t>67252</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31588</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>53778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29722</t>
+          <t>29477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>47450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65645</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95979</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50857</t>
+          <t>53037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47158</t>
+          <t>48230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>27015</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>48775</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53346</t>
+          <t>51879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43423</t>
+          <t>43219</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69014</t>
+          <t>67818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43533</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72349</t>
+          <t>73190</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104294</t>
+          <t>104792</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44366</t>
+          <t>43509</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43167</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66520</t>
+          <t>65870</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94501</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>129028</t>
+          <t>127445</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>40127</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>64529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55761</t>
+          <t>55794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79190</t>
+          <t>78650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114935</t>
+          <t>113409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109923</t>
+          <t>108403</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150036</t>
+          <t>149773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>128895</t>
+          <t>130895</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174256</t>
+          <t>176772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166133</t>
+          <t>163553</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209943</t>
+          <t>211163</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75639</t>
+          <t>74901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110535</t>
+          <t>110966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>251123</t>
+          <t>249770</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309622</t>
+          <t>308046</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>191894</t>
+          <t>192696</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>242997</t>
+          <t>241983</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128802</t>
+          <t>128040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166734</t>
+          <t>166211</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>334285</t>
+          <t>334259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>397475</t>
+          <t>398288</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>141854</t>
+          <t>139744</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>187411</t>
+          <t>186942</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>102930</t>
+          <t>103228</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>139379</t>
+          <t>140116</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>254596</t>
+          <t>256191</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>313914</t>
+          <t>312961</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2023</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2023 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42458</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55176</t>
+          <t>54075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51883</t>
+          <t>51709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72840</t>
+          <t>73236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28665</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>47571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14822</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>108844</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120773</t>
+          <t>118638</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150501</t>
+          <t>150661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27857</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164419</t>
+          <t>162482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99965</t>
+          <t>102835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113932</t>
+          <t>114691</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53655</t>
+          <t>55341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366474</t>
+          <t>368250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33370</t>
+          <t>33440</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94119</t>
+          <t>95026</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>417582</t>
+          <t>421061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>34780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>70176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26987</t>
+          <t>27829</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47314</t>
+          <t>48630</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>44840</t>
+          <t>44333</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>68774</t>
+          <t>68608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>30720</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70216</t>
+          <t>71774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58505</t>
+          <t>57467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44808</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66731</t>
+          <t>67141</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>41134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74953</t>
+          <t>74182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>101332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44526</t>
+          <t>46189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66979</t>
+          <t>69217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40999</t>
+          <t>41298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75457</t>
+          <t>76245</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102821</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59152</t>
+          <t>59944</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39481</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64616</t>
+          <t>63700</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>91945</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42671</t>
+          <t>43153</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>43705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50140</t>
+          <t>50392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>78815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82572</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255499</t>
+          <t>252611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57514</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>81746</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>124335</t>
+          <t>130566</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>318508</t>
+          <t>316228</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>83888</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>278991</t>
+          <t>281403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77953</t>
+          <t>77696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105226</t>
+          <t>103864</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155127</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>368675</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69339</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206081</t>
+          <t>206267</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72576</t>
+          <t>72525</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98129</t>
+          <t>100404</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122913</t>
+          <t>125977</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>294023</t>
+          <t>293024</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>119283</t>
+          <t>120136</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>591810</t>
+          <t>630142</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73655</t>
+          <t>75678</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>102448</t>
+          <t>105035</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>215406</t>
+          <t>216793</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>783181</t>
+          <t>765163</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>33851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50904</t>
+          <t>48491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56996</t>
+          <t>58329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51485</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69600</t>
+          <t>71226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34507</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>52780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35996</t>
+          <t>35178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41694</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65155</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>19091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49493</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79026</t>
+          <t>78367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>51308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77028</t>
+          <t>77167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>27126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46431</t>
+          <t>45907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85368</t>
+          <t>85508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118001</t>
+          <t>118241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35516</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59822</t>
+          <t>61785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58069</t>
+          <t>58321</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88946</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56598</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39171</t>
+          <t>39681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60980</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>49446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74186</t>
+          <t>74185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47385</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>43979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67787</t>
+          <t>69077</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55340</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74481</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63119</t>
+          <t>61413</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87293</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29150</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47998</t>
+          <t>47482</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96224</t>
+          <t>97266</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127354</t>
+          <t>128477</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47348</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>42083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56688</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>84397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83821</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59834</t>
+          <t>58464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93036</t>
+          <t>93149</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153144</t>
+          <t>151283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>196253</t>
+          <t>195034</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>53754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>189501</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>238140</t>
+          <t>238832</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>204423</t>
+          <t>204037</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250531</t>
+          <t>251539</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89833</t>
+          <t>91249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>303752</t>
+          <t>306450</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>364803</t>
+          <t>364462</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>124287</t>
+          <t>126793</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>166633</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>79418</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>108434</t>
+          <t>109802</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>211891</t>
+          <t>213966</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>265948</t>
+          <t>266848</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55109</t>
+          <t>54806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>34872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>62240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55258</t>
+          <t>54081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>36133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64865</t>
+          <t>62617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>50346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>77627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>38343</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77859</t>
+          <t>79437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109094</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21082</t>
+          <t>20902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>91811</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>57854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51371</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81102</t>
+          <t>81223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72757</t>
+          <t>75026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109266</t>
+          <t>106608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63412</t>
+          <t>62849</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93766</t>
+          <t>92557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>90880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125468</t>
+          <t>123690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55772</t>
+          <t>55715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>84232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>52188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92694</t>
+          <t>93150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129843</t>
+          <t>130415</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40506</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66392</t>
+          <t>65713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>25404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54289</t>
+          <t>53356</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85089</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55326</t>
+          <t>56706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59946</t>
+          <t>58868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75181</t>
+          <t>74615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108801</t>
+          <t>108882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38516</t>
+          <t>38362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64095</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51031</t>
+          <t>52959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75813</t>
+          <t>75967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108167</t>
+          <t>108330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>43494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,47 +5567,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>42435</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>30741</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>56015</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>17,7%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>42435</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>30669</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>55678</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58100</t>
+          <t>57988</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54465</t>
+          <t>54993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85793</t>
+          <t>84691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>61656</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89501</t>
+          <t>88291</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34980</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57072</t>
+          <t>56902</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102265</t>
+          <t>101144</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137606</t>
+          <t>135332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>41592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>68274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43221</t>
+          <t>42570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71437</t>
+          <t>69440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104453</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121911</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>170120</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>33108</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>142600</t>
+          <t>141344</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>194617</t>
+          <t>192631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>180631</t>
+          <t>179188</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>233647</t>
+          <t>231088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58551</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89857</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>247914</t>
+          <t>247177</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>310061</t>
+          <t>307876</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>232516</t>
+          <t>232320</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>285037</t>
+          <t>286406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132369</t>
+          <t>136168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>173771</t>
+          <t>172691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>379066</t>
+          <t>376453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>442840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>195806</t>
+          <t>197477</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>249507</t>
+          <t>249396</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>121524</t>
+          <t>123096</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>161109</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>334545</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>396541</t>
+          <t>403641</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>38287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29477</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51099</t>
+          <t>49933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37339</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>62102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53222</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80197</t>
+          <t>82099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15271</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34446</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61646</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49714</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35573</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61055</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>44006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70662</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,82 +7584,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>30628</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22069</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41342</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>29,52%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>21,27%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>87725</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>72551</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>104629</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>32,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>30628</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20821</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41880</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>29,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>40,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>87725</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>71136</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>103221</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>22,26%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61931</t>
+          <t>61966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91041</t>
+          <t>89965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43040</t>
+          <t>41590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>92147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124741</t>
+          <t>126029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>34902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59625</t>
+          <t>60095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41759</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93469</t>
+          <t>94584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37286</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>21243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42906</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25722</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>47584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>42996</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>67911</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53778</t>
+          <t>55135</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29477</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>47167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65863</t>
+          <t>66644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96974</t>
+          <t>95346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29591</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53037</t>
+          <t>52018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>49752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>75970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>26339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>47394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67818</t>
+          <t>68280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>45023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73190</t>
+          <t>71608</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104792</t>
+          <t>103791</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68633</t>
+          <t>68552</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65870</t>
+          <t>65470</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94263</t>
+          <t>90773</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127445</t>
+          <t>128051</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>40022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64529</t>
+          <t>65443</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55794</t>
+          <t>56686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78650</t>
+          <t>79364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113409</t>
+          <t>114306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108403</t>
+          <t>109491</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149773</t>
+          <t>150185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>130895</t>
+          <t>130094</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>176772</t>
+          <t>176517</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163553</t>
+          <t>162143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211163</t>
+          <t>212124</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74901</t>
+          <t>74728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110966</t>
+          <t>108990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249770</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308046</t>
+          <t>307742</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>192696</t>
+          <t>191268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>241983</t>
+          <t>239328</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128040</t>
+          <t>129602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166211</t>
+          <t>167809</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>334259</t>
+          <t>335128</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>398288</t>
+          <t>398442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>139744</t>
+          <t>142331</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>186942</t>
+          <t>187264</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>103228</t>
+          <t>102934</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>140116</t>
+          <t>138426</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>256191</t>
+          <t>253555</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>312961</t>
+          <t>313815</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>29289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>47257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>46395</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32799</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51867</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>37853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54075</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>61636</t>
+          <t>65644</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>54950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73236</t>
+          <t>77680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>23571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>39275</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113567</t>
+          <t>121833</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113567</t>
+          <t>121833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113567</t>
+          <t>121833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48716</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>162283</t>
+          <t>174185</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162283</t>
+          <t>174185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162283</t>
+          <t>174185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>44404</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108844</t>
+          <t>54896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>55531</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118638</t>
+          <t>75006</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54982</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>48506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150661</t>
+          <t>74020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>31136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22889</t>
+          <t>70692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162482</t>
+          <t>98220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102835</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>56576</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114691</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>268155</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55341</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>368250</t>
+          <t>37250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33440</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>294352</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>43375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>421061</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>397798</t>
+          <t>169906</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>397798</t>
+          <t>169906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397798</t>
+          <t>169906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>478973</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>478973</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>478973</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44447</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34780</t>
+          <t>36912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55314</t>
+          <t>58915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>57199</t>
+          <t>64133</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70176</t>
+          <t>77558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>43978</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>34268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48630</t>
+          <t>56201</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56352</t>
+          <t>65413</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>44333</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>68608</t>
+          <t>79494</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34886</t>
+          <t>42628</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24943</t>
+          <t>32719</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45017</t>
+          <t>55817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>57485</t>
+          <t>66716</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46043</t>
+          <t>53058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71774</t>
+          <t>79660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>28696</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>42338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>44030</t>
+          <t>50600</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32625</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>66103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>140780</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140780</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140780</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>83014</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>83014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>83014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>215066</t>
+          <t>246862</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215066</t>
+          <t>246862</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215066</t>
+          <t>246862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>55738</t>
+          <t>57309</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>46481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67141</t>
+          <t>69096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31964</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24383</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>87702</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74182</t>
+          <t>75473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101332</t>
+          <t>103264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>46194</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69217</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>44395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>93023</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76245</t>
+          <t>78829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>108157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>48814</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>62023</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>33849</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>43038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>77633</t>
+          <t>82663</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>69117</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91945</t>
+          <t>95859</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22194</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>36504</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>63808</t>
+          <t>69835</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>56187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78815</t>
+          <t>85471</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>189881</t>
+          <t>197505</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189881</t>
+          <t>197505</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>189881</t>
+          <t>197505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>127718</t>
+          <t>136859</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127718</t>
+          <t>136859</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127718</t>
+          <t>136859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>317599</t>
+          <t>334364</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317599</t>
+          <t>334364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>317599</t>
+          <t>334364</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>173448</t>
+          <t>188034</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>168553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>252611</t>
+          <t>210668</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>73590</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>61842</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81746</t>
+          <t>86758</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>242425</t>
+          <t>261623</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>130566</t>
+          <t>239437</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>316228</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>192534</t>
+          <t>209858</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83888</t>
+          <t>187794</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>281403</t>
+          <t>234168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>98102</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77696</t>
+          <t>85465</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103864</t>
+          <t>113307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>282972</t>
+          <t>307960</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151109</t>
+          <t>280379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>366919</t>
+          <t>333023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>153788</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>131853</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206267</t>
+          <t>173770</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>84915</t>
+          <t>91443</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72525</t>
+          <t>77842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100404</t>
+          <t>105971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>224844</t>
+          <t>245231</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>125977</t>
+          <t>220353</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>293024</t>
+          <t>272104</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>336115</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>120136</t>
+          <t>83236</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>630142</t>
+          <t>122653</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>87565</t>
+          <t>96772</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>75678</t>
+          <t>82780</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105035</t>
+          <t>113518</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>423679</t>
+          <t>198185</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>216793</t>
+          <t>173504</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>765163</t>
+          <t>225223</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>842026</t>
+          <t>653092</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>842026</t>
+          <t>653092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>842026</t>
+          <t>653092</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>331894</t>
+          <t>359907</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>331894</t>
+          <t>359907</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>331894</t>
+          <t>359907</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1173920</t>
+          <t>1012999</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1173920</t>
+          <t>1012999</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1173920</t>
+          <t>1012999</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
